--- a/Configs/GameConfig/Datas/global.xlsx
+++ b/Configs/GameConfig/Datas/global.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,6 +564,21 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>消除道具(清整行整列脱困道具)消耗体力</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/global.xlsx
+++ b/Configs/GameConfig/Datas/global.xlsx
@@ -540,12 +540,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1#10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>体力恢复时间(每点间隔秒)</t>
+          <t>体力恢复(点数#间隔秒)</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/global.xlsx
+++ b/Configs/GameConfig/Datas/global.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1#10</t>
+          <t>1#60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/Configs/GameConfig/Datas/global.xlsx
+++ b/Configs/GameConfig/Datas/global.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,6 +579,21 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>音频全局默认防连点时间(秒)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/global.xlsx
+++ b/Configs/GameConfig/Datas/global.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,21 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>女神满档清屏次数(积攒全清到此值可领取一次奖励,可循环)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
